--- a/resoluciones_comites.xlsx
+++ b/resoluciones_comites.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BD41E1-9747-4703-B08D-1A0BFB4A1B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E2E03-B425-4DD8-81B0-1F49EFEFB8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="368">
   <si>
     <t>Comité N°</t>
   </si>
@@ -639,9 +639,6 @@
     <t>0151-2023</t>
   </si>
   <si>
-    <t>0200-2025</t>
-  </si>
-  <si>
     <t>255</t>
   </si>
   <si>
@@ -675,15 +672,9 @@
     <t>265</t>
   </si>
   <si>
-    <t>0120-2021</t>
-  </si>
-  <si>
     <t>0244-2023</t>
   </si>
   <si>
-    <t>0255-2025</t>
-  </si>
-  <si>
     <t>268</t>
   </si>
   <si>
@@ -714,9 +705,6 @@
     <t>1443-2023</t>
   </si>
   <si>
-    <t>1175-2025</t>
-  </si>
-  <si>
     <t>273</t>
   </si>
   <si>
@@ -750,9 +738,6 @@
     <t>BUEN SOCORRO</t>
   </si>
   <si>
-    <t>1050-2020</t>
-  </si>
-  <si>
     <t>1713-2022</t>
   </si>
   <si>
@@ -777,9 +762,6 @@
     <t>0785-2020</t>
   </si>
   <si>
-    <t>1204-2022</t>
-  </si>
-  <si>
     <t>1174-2024</t>
   </si>
   <si>
@@ -840,24 +822,12 @@
     <t>313</t>
   </si>
   <si>
-    <t>DOMITILA CHINGANA</t>
-  </si>
-  <si>
-    <t>0512-2024</t>
-  </si>
-  <si>
-    <t>0750-2026</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
     <t>JERUSALEN MADRES UNIDAS</t>
   </si>
   <si>
-    <t>1168-2023</t>
-  </si>
-  <si>
     <t>1181-2025</t>
   </si>
   <si>
@@ -873,9 +843,6 @@
     <t>0035-2024</t>
   </si>
   <si>
-    <t>0295-2026</t>
-  </si>
-  <si>
     <t>340</t>
   </si>
   <si>
@@ -900,12 +867,6 @@
     <t>1812-2021</t>
   </si>
   <si>
-    <t>0048-2024</t>
-  </si>
-  <si>
-    <t>0207-2026</t>
-  </si>
-  <si>
     <t>360</t>
   </si>
   <si>
@@ -927,24 +888,15 @@
     <t>RAMIRO PRIALE PRIALE</t>
   </si>
   <si>
-    <t>0643-2021</t>
-  </si>
-  <si>
     <t>0793-2023</t>
   </si>
   <si>
-    <t>0625-2025</t>
-  </si>
-  <si>
     <t>370</t>
   </si>
   <si>
     <t>JEHOVA ES MI PASTOR</t>
   </si>
   <si>
-    <t>0746-2020</t>
-  </si>
-  <si>
     <t>1244-2022</t>
   </si>
   <si>
@@ -963,18 +915,12 @@
     <t>0046-2024</t>
   </si>
   <si>
-    <t>0240-2026</t>
-  </si>
-  <si>
     <t>378</t>
   </si>
   <si>
     <t>EL ANGEL</t>
   </si>
   <si>
-    <t>0830-2024</t>
-  </si>
-  <si>
     <t>380</t>
   </si>
   <si>
@@ -1126,6 +1072,66 @@
   </si>
   <si>
     <t>0920-2021</t>
+  </si>
+  <si>
+    <t>0260-2025</t>
+  </si>
+  <si>
+    <t>0265-2026</t>
+  </si>
+  <si>
+    <t>0126-2021</t>
+  </si>
+  <si>
+    <t>0299-2025</t>
+  </si>
+  <si>
+    <t>0630-2024</t>
+  </si>
+  <si>
+    <t>1179-2025</t>
+  </si>
+  <si>
+    <t>1060-2020</t>
+  </si>
+  <si>
+    <t>1264-2022</t>
+  </si>
+  <si>
+    <t>DOMITILA CHUNGARA</t>
+  </si>
+  <si>
+    <t>0612-2024</t>
+  </si>
+  <si>
+    <t>0416-2023</t>
+  </si>
+  <si>
+    <t>0756-2026</t>
+  </si>
+  <si>
+    <t>1163-2023</t>
+  </si>
+  <si>
+    <t>0296-2026</t>
+  </si>
+  <si>
+    <t>0267-2026</t>
+  </si>
+  <si>
+    <t>0825-2025</t>
+  </si>
+  <si>
+    <t>0543-2021</t>
+  </si>
+  <si>
+    <t>0745-2020</t>
+  </si>
+  <si>
+    <t>0340-2026</t>
+  </si>
+  <si>
+    <t>0749-2026</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1542,7 @@
         <v>45158</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1553,7 +1559,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="F3" s="4">
         <v>45166</v>
@@ -1562,7 +1568,7 @@
         <v>45897</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1579,7 +1585,7 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="F4" s="4">
         <v>45958</v>
@@ -1588,7 +1594,7 @@
         <v>46688</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1614,7 +1620,7 @@
         <v>46649</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1640,7 +1646,7 @@
         <v>46201</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1648,7 +1654,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1684,7 +1690,7 @@
         <v>46649</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1710,7 +1716,7 @@
         <v>45387</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1727,7 +1733,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F10" s="4">
         <v>45471</v>
@@ -1736,7 +1742,7 @@
         <v>46201</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1762,7 +1768,7 @@
         <v>46970</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1788,7 +1794,7 @@
         <v>46379</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1814,7 +1820,7 @@
         <v>45156</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1831,7 +1837,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F14" s="4">
         <v>45194</v>
@@ -1840,7 +1846,7 @@
         <v>45925</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1866,7 +1872,7 @@
         <v>46711</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1883,7 +1889,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="F16" s="4">
         <v>44069</v>
@@ -1892,7 +1898,7 @@
         <v>44799</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1918,7 +1924,7 @@
         <v>45577</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1944,7 +1950,7 @@
         <v>46358</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1970,7 +1976,7 @@
         <v>45582</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1996,7 +2002,7 @@
         <v>46339</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2022,7 +2028,7 @@
         <v>45761</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -2048,7 +2054,7 @@
         <v>46534</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2074,7 +2080,7 @@
         <v>45684</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -2100,7 +2106,7 @@
         <v>46449</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2126,7 +2132,7 @@
         <v>45863</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2152,7 +2158,7 @@
         <v>46619</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2169,7 +2175,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="F27" s="4">
         <v>46170</v>
@@ -2178,7 +2184,7 @@
         <v>46901</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2204,7 +2210,7 @@
         <v>44902</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2230,7 +2236,7 @@
         <v>45684</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -2256,7 +2262,7 @@
         <v>46446</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2273,7 +2279,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="F31" s="4">
         <v>44379</v>
@@ -2282,7 +2288,7 @@
         <v>45109</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2299,7 +2305,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="F32" s="4">
         <v>45182</v>
@@ -2308,7 +2314,7 @@
         <v>45913</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -2334,7 +2340,7 @@
         <v>46677</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -2342,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
@@ -2351,7 +2357,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="F34" s="4">
         <v>43857</v>
@@ -2360,7 +2366,7 @@
         <v>44588</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -2368,7 +2374,7 @@
         <v>64</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>13</v>
@@ -2386,7 +2392,7 @@
         <v>45343</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -2394,7 +2400,7 @@
         <v>64</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>15</v>
@@ -2412,7 +2418,7 @@
         <v>46194</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -2438,7 +2444,7 @@
         <v>46473</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -2464,7 +2470,7 @@
         <v>45350</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -2490,7 +2496,7 @@
         <v>46103</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -2516,7 +2522,7 @@
         <v>46866</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -2542,7 +2548,7 @@
         <v>45912</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2568,7 +2574,7 @@
         <v>46677</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2594,7 +2600,7 @@
         <v>44902</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -2620,7 +2626,7 @@
         <v>45649</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -2637,7 +2643,7 @@
         <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F45" s="4">
         <v>45701</v>
@@ -2646,7 +2652,7 @@
         <v>46431</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -2672,7 +2678,7 @@
         <v>45277</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -2698,7 +2704,7 @@
         <v>46037</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -2724,7 +2730,7 @@
         <v>46807</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -2750,7 +2756,7 @@
         <v>45428</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -2767,7 +2773,7 @@
         <v>14</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="F50" s="4">
         <v>45483</v>
@@ -2776,7 +2782,7 @@
         <v>46213</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -2802,7 +2808,7 @@
         <v>46982</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -2828,7 +2834,7 @@
         <v>45116</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -2854,7 +2860,7 @@
         <v>45941</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -2880,7 +2886,7 @@
         <v>46725</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -2906,7 +2912,7 @@
         <v>46006</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -2932,7 +2938,7 @@
         <v>46768</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -2958,7 +2964,7 @@
         <v>44834</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -2984,7 +2990,7 @@
         <v>45619</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -3010,7 +3016,7 @@
         <v>46387</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
@@ -3036,7 +3042,7 @@
         <v>45697</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
@@ -3053,7 +3059,7 @@
         <v>14</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="F61" s="4">
         <v>45429</v>
@@ -3062,7 +3068,7 @@
         <v>46159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -3079,7 +3085,7 @@
         <v>14</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="F62" s="4">
         <v>45733</v>
@@ -3088,7 +3094,7 @@
         <v>46463</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -3114,7 +3120,7 @@
         <v>45277</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
@@ -3131,7 +3137,7 @@
         <v>14</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="F64" s="4">
         <v>45313</v>
@@ -3140,7 +3146,7 @@
         <v>46044</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
@@ -3166,7 +3172,7 @@
         <v>46842</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -3192,7 +3198,7 @@
         <v>45001</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3218,7 +3224,7 @@
         <v>45768</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -3235,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="F68" s="4">
         <v>45807</v>
@@ -3244,7 +3250,7 @@
         <v>46537</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3261,7 +3267,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="F69" s="4">
         <v>44379</v>
@@ -3270,7 +3276,7 @@
         <v>45109</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3296,7 +3302,7 @@
         <v>45880</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -3313,7 +3319,7 @@
         <v>14</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="F71" s="4">
         <v>45905</v>
@@ -3322,7 +3328,7 @@
         <v>46635</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3339,7 +3345,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="F72" s="4">
         <v>44223</v>
@@ -3348,7 +3354,7 @@
         <v>44953</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -3374,7 +3380,7 @@
         <v>45549</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
@@ -3400,7 +3406,7 @@
         <v>46332</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -3417,7 +3423,7 @@
         <v>11</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="F75" s="4">
         <v>45533</v>
@@ -3426,7 +3432,7 @@
         <v>46263</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
@@ -3443,7 +3449,7 @@
         <v>11</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="F76" s="4">
         <v>44823</v>
@@ -3452,7 +3458,7 @@
         <v>45554</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
@@ -3478,7 +3484,7 @@
         <v>45619</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -3504,7 +3510,7 @@
         <v>46305</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -3530,7 +3536,7 @@
         <v>44834</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -3556,7 +3562,7 @@
         <v>45582</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -3582,7 +3588,7 @@
         <v>46387</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
@@ -3599,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F82" s="4">
         <v>44532</v>
@@ -3608,7 +3614,7 @@
         <v>45262</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
@@ -3634,7 +3640,7 @@
         <v>46044</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -3660,7 +3666,7 @@
         <v>46830</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -3677,7 +3683,7 @@
         <v>11</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="F85" s="4">
         <v>44705</v>
@@ -3686,7 +3692,7 @@
         <v>45436</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
@@ -3712,7 +3718,7 @@
         <v>46197</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -3729,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="F87" s="4">
         <v>46237</v>
@@ -3738,7 +3744,7 @@
         <v>46968</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -3755,7 +3761,7 @@
         <v>11</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="F88" s="4">
         <v>44918</v>
@@ -3764,7 +3770,7 @@
         <v>45649</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -3790,7 +3796,7 @@
         <v>46038</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -3807,7 +3813,7 @@
         <v>14</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="F90" s="4">
         <v>46094</v>
@@ -3816,7 +3822,7 @@
         <v>46825</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -3824,7 +3830,7 @@
         <v>146</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>10</v>
@@ -3833,7 +3839,7 @@
         <v>11</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F91" s="4">
         <v>44258</v>
@@ -3842,7 +3848,7 @@
         <v>44988</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -3850,7 +3856,7 @@
         <v>146</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>13</v>
@@ -3868,7 +3874,7 @@
         <v>45759</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -3876,7 +3882,7 @@
         <v>146</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>15</v>
@@ -3885,7 +3891,7 @@
         <v>14</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F93" s="4">
         <v>45799</v>
@@ -3894,7 +3900,7 @@
         <v>46529</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -3920,7 +3926,7 @@
         <v>45274</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -3946,7 +3952,7 @@
         <v>46045</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -3972,7 +3978,7 @@
         <v>46825</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -3998,7 +4004,7 @@
         <v>45360</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -4024,7 +4030,7 @@
         <v>46162</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -4050,7 +4056,7 @@
         <v>46913</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -4070,13 +4076,13 @@
         <v>160</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="G100" s="4">
         <v>45270</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
@@ -4093,7 +4099,7 @@
         <v>14</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="F101" s="4">
         <v>45300</v>
@@ -4102,7 +4108,7 @@
         <v>46031</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -4119,7 +4125,7 @@
         <v>14</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="F102" s="4">
         <v>46083</v>
@@ -4128,7 +4134,7 @@
         <v>46814</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -4154,7 +4160,7 @@
         <v>45277</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
@@ -4180,7 +4186,7 @@
         <v>46037</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -4206,7 +4212,7 @@
         <v>46807</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
@@ -4232,7 +4238,7 @@
         <v>45219</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
@@ -4249,7 +4255,7 @@
         <v>14</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F107" s="4">
         <v>45257</v>
@@ -4258,7 +4264,7 @@
         <v>45988</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -4284,7 +4290,7 @@
         <v>46744</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -4310,7 +4316,7 @@
         <v>45343</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -4327,7 +4333,7 @@
         <v>14</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="F110" s="4">
         <v>45442</v>
@@ -4336,7 +4342,7 @@
         <v>46172</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -4353,7 +4359,7 @@
         <v>14</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F111" s="4">
         <v>46245</v>
@@ -4362,7 +4368,7 @@
         <v>46976</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
@@ -4388,7 +4394,7 @@
         <v>45109</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -4414,7 +4420,7 @@
         <v>45913</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
@@ -4431,7 +4437,7 @@
         <v>14</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="F114" s="4">
         <v>45954</v>
@@ -4440,7 +4446,7 @@
         <v>46684</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4457,7 +4463,7 @@
         <v>11</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="F115" s="4">
         <v>44428</v>
@@ -4466,7 +4472,7 @@
         <v>45158</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
@@ -4492,7 +4498,7 @@
         <v>45974</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
@@ -4518,7 +4524,7 @@
         <v>46775</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4543,7 +4549,9 @@
       <c r="G118" s="4">
         <v>46463</v>
       </c>
-      <c r="H118" s="3"/>
+      <c r="H118" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
@@ -4562,12 +4570,14 @@
         <v>186</v>
       </c>
       <c r="F119" s="4">
-        <v>46217</v>
+        <v>44613</v>
       </c>
       <c r="G119" s="4">
-        <v>46948</v>
-      </c>
-      <c r="H119" s="3"/>
+        <v>45343</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
@@ -4586,12 +4596,14 @@
         <v>187</v>
       </c>
       <c r="F120" s="4">
-        <v>46217</v>
+        <v>45440</v>
       </c>
       <c r="G120" s="4">
-        <v>46948</v>
-      </c>
-      <c r="H120" s="3"/>
+        <v>46170</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
@@ -4615,7 +4627,9 @@
       <c r="G121" s="4">
         <v>46948</v>
       </c>
-      <c r="H121" s="3"/>
+      <c r="H121" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
@@ -4634,12 +4648,14 @@
         <v>191</v>
       </c>
       <c r="F122" s="4">
-        <v>45789</v>
+        <v>44257</v>
       </c>
       <c r="G122" s="4">
-        <v>46519</v>
-      </c>
-      <c r="H122" s="3"/>
+        <v>44987</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
@@ -4658,12 +4674,14 @@
         <v>192</v>
       </c>
       <c r="F123" s="4">
-        <v>45789</v>
+        <v>45043</v>
       </c>
       <c r="G123" s="4">
-        <v>46519</v>
-      </c>
-      <c r="H123" s="3"/>
+        <v>45774</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
@@ -4687,7 +4705,9 @@
       <c r="G124" s="4">
         <v>46519</v>
       </c>
-      <c r="H124" s="3"/>
+      <c r="H124" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
@@ -4706,12 +4726,14 @@
         <v>196</v>
       </c>
       <c r="F125" s="4">
-        <v>45604</v>
+        <v>44042</v>
       </c>
       <c r="G125" s="4">
-        <v>46334</v>
-      </c>
-      <c r="H125" s="3"/>
+        <v>44772</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
@@ -4730,12 +4752,14 @@
         <v>197</v>
       </c>
       <c r="F126" s="4">
-        <v>45604</v>
+        <v>44841</v>
       </c>
       <c r="G126" s="4">
-        <v>46334</v>
-      </c>
-      <c r="H126" s="3"/>
+        <v>45572</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
@@ -4759,7 +4783,9 @@
       <c r="G127" s="4">
         <v>46334</v>
       </c>
-      <c r="H127" s="3"/>
+      <c r="H127" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
@@ -4783,7 +4809,9 @@
       <c r="G128" s="4">
         <v>46453</v>
       </c>
-      <c r="H128" s="3"/>
+      <c r="H128" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
@@ -4802,12 +4830,14 @@
         <v>202</v>
       </c>
       <c r="F129" s="4">
-        <v>45723</v>
+        <v>44165</v>
       </c>
       <c r="G129" s="4">
-        <v>46453</v>
-      </c>
-      <c r="H129" s="3"/>
+        <v>44895</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
@@ -4823,7 +4853,7 @@
         <v>14</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>203</v>
+        <v>348</v>
       </c>
       <c r="F130" s="4">
         <v>45723</v>
@@ -4831,38 +4861,42 @@
       <c r="G130" s="4">
         <v>46453</v>
       </c>
-      <c r="H130" s="3"/>
+      <c r="H130" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F131" s="4">
-        <v>45630</v>
+        <v>44104</v>
       </c>
       <c r="G131" s="4">
-        <v>46360</v>
-      </c>
-      <c r="H131" s="3"/>
+        <v>44834</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>13</v>
@@ -4871,22 +4905,24 @@
         <v>14</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F132" s="4">
+        <v>44882</v>
+      </c>
+      <c r="G132" s="4">
         <v>45630</v>
       </c>
-      <c r="G132" s="4">
-        <v>46360</v>
-      </c>
-      <c r="H132" s="3"/>
+      <c r="H132" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>15</v>
@@ -4895,7 +4931,7 @@
         <v>14</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F133" s="4">
         <v>45630</v>
@@ -4903,38 +4939,42 @@
       <c r="G133" s="4">
         <v>46360</v>
       </c>
-      <c r="H133" s="3"/>
+      <c r="H133" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="C134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F134" s="4">
-        <v>45706</v>
+        <v>44172</v>
       </c>
       <c r="G134" s="4">
-        <v>46436</v>
-      </c>
-      <c r="H134" s="3"/>
+        <v>44182</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>13</v>
@@ -4943,22 +4983,24 @@
         <v>14</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F135" s="4">
-        <v>45706</v>
+        <v>44953</v>
       </c>
       <c r="G135" s="4">
-        <v>46436</v>
-      </c>
-      <c r="H135" s="3"/>
+        <v>45684</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>15</v>
@@ -4967,7 +5009,7 @@
         <v>14</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F136" s="4">
         <v>45706</v>
@@ -4975,11 +5017,13 @@
       <c r="G136" s="4">
         <v>46436</v>
       </c>
-      <c r="H136" s="3"/>
+      <c r="H136" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>136</v>
@@ -4991,19 +5035,21 @@
         <v>11</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>215</v>
+        <v>350</v>
       </c>
       <c r="F137" s="4">
-        <v>45740</v>
+        <v>44232</v>
       </c>
       <c r="G137" s="4">
-        <v>46470</v>
-      </c>
-      <c r="H137" s="3"/>
+        <v>44962</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>136</v>
@@ -5015,19 +5061,21 @@
         <v>14</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F138" s="4">
-        <v>45740</v>
+        <v>44977</v>
       </c>
       <c r="G138" s="4">
-        <v>46470</v>
-      </c>
-      <c r="H138" s="3"/>
+        <v>45708</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>136</v>
@@ -5039,7 +5087,7 @@
         <v>14</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>217</v>
+        <v>351</v>
       </c>
       <c r="F139" s="4">
         <v>45740</v>
@@ -5047,14 +5095,16 @@
       <c r="G139" s="4">
         <v>46470</v>
       </c>
-      <c r="H139" s="3"/>
+      <c r="H139" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>10</v>
@@ -5063,7 +5113,7 @@
         <v>11</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F140" s="4">
         <v>45917</v>
@@ -5071,11 +5121,13 @@
       <c r="G140" s="4">
         <v>46647</v>
       </c>
-      <c r="H140" s="3"/>
+      <c r="H140" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>136</v>
@@ -5087,19 +5139,21 @@
         <v>11</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F141" s="4">
-        <v>45751</v>
+        <v>44196</v>
       </c>
       <c r="G141" s="4">
-        <v>46481</v>
-      </c>
-      <c r="H141" s="3"/>
+        <v>44926</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>136</v>
@@ -5111,19 +5165,21 @@
         <v>14</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F142" s="4">
-        <v>45751</v>
+        <v>44973</v>
       </c>
       <c r="G142" s="4">
-        <v>46481</v>
-      </c>
-      <c r="H142" s="3"/>
+        <v>45704</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>136</v>
@@ -5135,7 +5191,7 @@
         <v>14</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F143" s="4">
         <v>45751</v>
@@ -5143,14 +5199,16 @@
       <c r="G143" s="4">
         <v>46481</v>
       </c>
-      <c r="H143" s="3"/>
+      <c r="H143" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>10</v>
@@ -5159,22 +5217,24 @@
         <v>11</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F144" s="4">
-        <v>45968</v>
+        <v>45224</v>
       </c>
       <c r="G144" s="4">
-        <v>46698</v>
-      </c>
-      <c r="H144" s="3"/>
+        <v>45955</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>13</v>
@@ -5183,7 +5243,7 @@
         <v>14</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>228</v>
+        <v>353</v>
       </c>
       <c r="F145" s="4">
         <v>45968</v>
@@ -5191,14 +5251,16 @@
       <c r="G145" s="4">
         <v>46698</v>
       </c>
-      <c r="H145" s="3"/>
+      <c r="H145" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>10</v>
@@ -5207,22 +5269,24 @@
         <v>11</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F146" s="4">
-        <v>45721</v>
+        <v>44953</v>
       </c>
       <c r="G146" s="4">
-        <v>46451</v>
-      </c>
-      <c r="H146" s="3"/>
+        <v>44953</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>13</v>
@@ -5231,22 +5295,24 @@
         <v>14</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F147" s="4">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G147" s="4">
-        <v>46451</v>
-      </c>
-      <c r="H147" s="3"/>
+        <v>46452</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>10</v>
@@ -5255,22 +5321,24 @@
         <v>11</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F148" s="4">
-        <v>45700</v>
+        <v>44918</v>
       </c>
       <c r="G148" s="4">
-        <v>46430</v>
-      </c>
-      <c r="H148" s="3"/>
+        <v>45649</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>13</v>
@@ -5279,22 +5347,24 @@
         <v>14</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F149" s="4">
-        <v>45700</v>
+        <v>45096</v>
       </c>
       <c r="G149" s="4">
-        <v>46430</v>
-      </c>
-      <c r="H149" s="3"/>
+        <v>45827</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>15</v>
@@ -5303,7 +5373,7 @@
         <v>14</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F150" s="4">
         <v>45700</v>
@@ -5311,14 +5381,16 @@
       <c r="G150" s="4">
         <v>46430</v>
       </c>
-      <c r="H150" s="3"/>
+      <c r="H150" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>10</v>
@@ -5327,22 +5399,24 @@
         <v>11</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>240</v>
+        <v>354</v>
       </c>
       <c r="F151" s="4">
-        <v>45700</v>
+        <v>44165</v>
       </c>
       <c r="G151" s="4">
-        <v>46430</v>
-      </c>
-      <c r="H151" s="3"/>
+        <v>44895</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>13</v>
@@ -5351,22 +5425,24 @@
         <v>14</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F152" s="4">
-        <v>45700</v>
+        <v>44918</v>
       </c>
       <c r="G152" s="4">
-        <v>46430</v>
-      </c>
-      <c r="H152" s="3"/>
+        <v>45649</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>15</v>
@@ -5375,7 +5451,7 @@
         <v>14</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F153" s="4">
         <v>45700</v>
@@ -5383,14 +5459,16 @@
       <c r="G153" s="4">
         <v>46430</v>
       </c>
-      <c r="H153" s="3"/>
+      <c r="H153" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>10</v>
@@ -5399,7 +5477,7 @@
         <v>11</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F154" s="4">
         <v>45618</v>
@@ -5407,14 +5485,16 @@
       <c r="G154" s="4">
         <v>46348</v>
       </c>
-      <c r="H154" s="3"/>
+      <c r="H154" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>10</v>
@@ -5423,22 +5503,24 @@
         <v>11</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F155" s="4">
-        <v>45618</v>
+        <v>44103</v>
       </c>
       <c r="G155" s="4">
-        <v>46348</v>
-      </c>
-      <c r="H155" s="3"/>
+        <v>44833</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>13</v>
@@ -5447,22 +5529,24 @@
         <v>14</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="F156" s="4">
-        <v>45618</v>
+        <v>44862</v>
       </c>
       <c r="G156" s="4">
-        <v>46348</v>
-      </c>
-      <c r="H156" s="3"/>
+        <v>45593</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>15</v>
@@ -5471,7 +5555,7 @@
         <v>14</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F157" s="4">
         <v>45618</v>
@@ -5479,14 +5563,16 @@
       <c r="G157" s="4">
         <v>46348</v>
       </c>
-      <c r="H157" s="3"/>
+      <c r="H157" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>10</v>
@@ -5495,22 +5581,24 @@
         <v>11</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F158" s="4">
-        <v>46120</v>
+        <v>44613</v>
       </c>
       <c r="G158" s="4">
-        <v>46851</v>
-      </c>
-      <c r="H158" s="3"/>
+        <v>45343</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>13</v>
@@ -5519,22 +5607,24 @@
         <v>14</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F159" s="4">
-        <v>46120</v>
+        <v>45377</v>
       </c>
       <c r="G159" s="4">
-        <v>46851</v>
-      </c>
-      <c r="H159" s="3"/>
+        <v>46107</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>15</v>
@@ -5543,7 +5633,7 @@
         <v>14</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F160" s="4">
         <v>46120</v>
@@ -5551,14 +5641,16 @@
       <c r="G160" s="4">
         <v>46851</v>
       </c>
-      <c r="H160" s="3"/>
+      <c r="H160" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>10</v>
@@ -5567,22 +5659,24 @@
         <v>11</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F161" s="4">
-        <v>45978</v>
+        <v>44426</v>
       </c>
       <c r="G161" s="4">
-        <v>46708</v>
-      </c>
-      <c r="H161" s="3"/>
+        <v>45156</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>13</v>
@@ -5591,22 +5685,24 @@
         <v>14</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F162" s="4">
-        <v>45978</v>
+        <v>45219</v>
       </c>
       <c r="G162" s="4">
-        <v>46708</v>
-      </c>
-      <c r="H162" s="3"/>
+        <v>45950</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>15</v>
@@ -5615,7 +5711,7 @@
         <v>14</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F163" s="4">
         <v>45978</v>
@@ -5623,14 +5719,16 @@
       <c r="G163" s="4">
         <v>46708</v>
       </c>
-      <c r="H163" s="3"/>
+      <c r="H163" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>10</v>
@@ -5639,22 +5737,24 @@
         <v>11</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F164" s="4">
-        <v>45744</v>
+        <v>44979</v>
       </c>
       <c r="G164" s="4">
-        <v>46474</v>
-      </c>
-      <c r="H164" s="3"/>
+        <v>45710</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>13</v>
@@ -5663,7 +5763,7 @@
         <v>14</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F165" s="4">
         <v>45744</v>
@@ -5671,14 +5771,16 @@
       <c r="G165" s="4">
         <v>46474</v>
       </c>
-      <c r="H165" s="3"/>
+      <c r="H165" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>10</v>
@@ -5687,22 +5789,24 @@
         <v>11</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F166" s="4">
-        <v>46077</v>
+        <v>44519</v>
       </c>
       <c r="G166" s="4">
-        <v>46807</v>
-      </c>
-      <c r="H166" s="3"/>
+        <v>45249</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>13</v>
@@ -5711,22 +5815,24 @@
         <v>14</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F167" s="4">
-        <v>46077</v>
+        <v>45302</v>
       </c>
       <c r="G167" s="4">
-        <v>46807</v>
-      </c>
-      <c r="H167" s="3"/>
+        <v>46033</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>15</v>
@@ -5743,14 +5849,16 @@
       <c r="G168" s="4">
         <v>46807</v>
       </c>
-      <c r="H168" s="3"/>
+      <c r="H168" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>10</v>
@@ -5759,7 +5867,7 @@
         <v>11</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>50</v>
+        <v>358</v>
       </c>
       <c r="F169" s="4">
         <v>46253</v>
@@ -5767,14 +5875,16 @@
       <c r="G169" s="4">
         <v>46984</v>
       </c>
-      <c r="H169" s="3"/>
+      <c r="H169" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>13</v>
@@ -5783,22 +5893,24 @@
         <v>14</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
       <c r="F170" s="4">
-        <v>46253</v>
+        <v>45485</v>
       </c>
       <c r="G170" s="4">
-        <v>46984</v>
-      </c>
-      <c r="H170" s="3"/>
+        <v>46215</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>15</v>
@@ -5807,7 +5919,7 @@
         <v>14</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>272</v>
+        <v>359</v>
       </c>
       <c r="F171" s="4">
         <v>46253</v>
@@ -5815,14 +5927,16 @@
       <c r="G171" s="4">
         <v>46984</v>
       </c>
-      <c r="H171" s="3"/>
+      <c r="H171" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>10</v>
@@ -5831,22 +5945,24 @@
         <v>11</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>275</v>
+        <v>360</v>
       </c>
       <c r="F172" s="4">
-        <v>45968</v>
+        <v>45181</v>
       </c>
       <c r="G172" s="4">
-        <v>46698</v>
-      </c>
-      <c r="H172" s="3"/>
+        <v>45912</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>13</v>
@@ -5855,7 +5971,7 @@
         <v>14</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F173" s="4">
         <v>45968</v>
@@ -5863,14 +5979,16 @@
       <c r="G173" s="4">
         <v>46698</v>
       </c>
-      <c r="H173" s="3"/>
+      <c r="H173" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>10</v>
@@ -5879,22 +5997,24 @@
         <v>11</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F174" s="4">
-        <v>46101</v>
+        <v>44540</v>
       </c>
       <c r="G174" s="4">
-        <v>46832</v>
-      </c>
-      <c r="H174" s="3"/>
+        <v>45270</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>13</v>
@@ -5903,22 +6023,24 @@
         <v>14</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F175" s="4">
-        <v>46101</v>
+        <v>45310</v>
       </c>
       <c r="G175" s="4">
-        <v>46832</v>
-      </c>
-      <c r="H175" s="3"/>
+        <v>46041</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>15</v>
@@ -5927,7 +6049,7 @@
         <v>14</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="F176" s="4">
         <v>46101</v>
@@ -5935,14 +6057,16 @@
       <c r="G176" s="4">
         <v>46832</v>
       </c>
-      <c r="H176" s="3"/>
+      <c r="H176" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>10</v>
@@ -5951,22 +6075,24 @@
         <v>11</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="F177" s="4">
-        <v>45968</v>
+        <v>44448</v>
       </c>
       <c r="G177" s="4">
-        <v>46698</v>
-      </c>
-      <c r="H177" s="3"/>
+        <v>44448</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>13</v>
@@ -5975,22 +6101,24 @@
         <v>14</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="F178" s="4">
-        <v>45968</v>
+        <v>45194</v>
       </c>
       <c r="G178" s="4">
-        <v>46698</v>
-      </c>
-      <c r="H178" s="3"/>
+        <v>45925</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>15</v>
@@ -5999,7 +6127,7 @@
         <v>14</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="F179" s="4">
         <v>45968</v>
@@ -6007,14 +6135,16 @@
       <c r="G179" s="4">
         <v>46698</v>
       </c>
-      <c r="H179" s="3"/>
+      <c r="H179" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>10</v>
@@ -6023,22 +6153,24 @@
         <v>11</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F180" s="4">
-        <v>46094</v>
+        <v>44557</v>
       </c>
       <c r="G180" s="4">
-        <v>46825</v>
-      </c>
-      <c r="H180" s="3"/>
+        <v>45287</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>13</v>
@@ -6047,22 +6179,24 @@
         <v>14</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F181" s="4">
-        <v>46094</v>
+        <v>45314</v>
       </c>
       <c r="G181" s="4">
-        <v>46825</v>
-      </c>
-      <c r="H181" s="3"/>
+        <v>46045</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>15</v>
@@ -6071,7 +6205,7 @@
         <v>14</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>291</v>
+        <v>362</v>
       </c>
       <c r="F182" s="4">
         <v>46094</v>
@@ -6079,14 +6213,16 @@
       <c r="G182" s="4">
         <v>46825</v>
       </c>
-      <c r="H182" s="3"/>
+      <c r="H182" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>10</v>
@@ -6095,22 +6231,24 @@
         <v>11</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="F183" s="4">
-        <v>45616</v>
+        <v>44099</v>
       </c>
       <c r="G183" s="4">
-        <v>46346</v>
-      </c>
-      <c r="H183" s="3"/>
+        <v>44829</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>13</v>
@@ -6119,22 +6257,24 @@
         <v>14</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="F184" s="4">
-        <v>45616</v>
+        <v>44859</v>
       </c>
       <c r="G184" s="4">
-        <v>46346</v>
-      </c>
-      <c r="H184" s="3"/>
+        <v>45590</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>15</v>
@@ -6143,7 +6283,7 @@
         <v>14</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="F185" s="4">
         <v>45616</v>
@@ -6151,14 +6291,16 @@
       <c r="G185" s="4">
         <v>46346</v>
       </c>
-      <c r="H185" s="3"/>
+      <c r="H185" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>10</v>
@@ -6167,22 +6309,24 @@
         <v>11</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="F186" s="4">
-        <v>45860</v>
+        <v>44342</v>
       </c>
       <c r="G186" s="4">
-        <v>46590</v>
-      </c>
-      <c r="H186" s="3"/>
+        <v>45072</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>13</v>
@@ -6191,22 +6335,24 @@
         <v>14</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="F187" s="4">
-        <v>45860</v>
+        <v>45103</v>
       </c>
       <c r="G187" s="4">
-        <v>46590</v>
-      </c>
-      <c r="H187" s="3"/>
+        <v>45834</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>15</v>
@@ -6215,7 +6361,7 @@
         <v>14</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="F188" s="4">
         <v>45860</v>
@@ -6223,14 +6369,16 @@
       <c r="G188" s="4">
         <v>46590</v>
       </c>
-      <c r="H188" s="3"/>
+      <c r="H188" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>10</v>
@@ -6239,22 +6387,24 @@
         <v>11</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="F189" s="4">
-        <v>45639</v>
+        <v>44092</v>
       </c>
       <c r="G189" s="4">
-        <v>46369</v>
-      </c>
-      <c r="H189" s="3"/>
+        <v>44822</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>13</v>
@@ -6263,22 +6413,24 @@
         <v>14</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="F190" s="4">
-        <v>45639</v>
+        <v>44854</v>
       </c>
       <c r="G190" s="4">
-        <v>46369</v>
-      </c>
-      <c r="H190" s="3"/>
+        <v>45585</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>15</v>
@@ -6287,7 +6439,7 @@
         <v>14</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="F191" s="4">
         <v>45639</v>
@@ -6295,14 +6447,16 @@
       <c r="G191" s="4">
         <v>46369</v>
       </c>
-      <c r="H191" s="3"/>
+      <c r="H191" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>10</v>
@@ -6311,22 +6465,24 @@
         <v>11</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="F192" s="4">
-        <v>46121</v>
+        <v>44540</v>
       </c>
       <c r="G192" s="4">
-        <v>46851</v>
-      </c>
-      <c r="H192" s="3"/>
+        <v>45270</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>13</v>
@@ -6335,22 +6491,24 @@
         <v>14</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="F193" s="4">
-        <v>46121</v>
+        <v>45314</v>
       </c>
       <c r="G193" s="4">
-        <v>46851</v>
-      </c>
-      <c r="H193" s="3"/>
+        <v>46045</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>15</v>
@@ -6359,7 +6517,7 @@
         <v>14</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="F194" s="4">
         <v>46121</v>
@@ -6367,14 +6525,16 @@
       <c r="G194" s="4">
         <v>46851</v>
       </c>
-      <c r="H194" s="3"/>
+      <c r="H194" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>10</v>
@@ -6383,22 +6543,24 @@
         <v>11</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="F195" s="4">
-        <v>46251</v>
+        <v>45492</v>
       </c>
       <c r="G195" s="4">
-        <v>46982</v>
-      </c>
-      <c r="H195" s="3"/>
+        <v>46222</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>13</v>
@@ -6407,7 +6569,7 @@
         <v>14</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>91</v>
+        <v>367</v>
       </c>
       <c r="F196" s="4">
         <v>46251</v>
@@ -6415,14 +6577,16 @@
       <c r="G196" s="4">
         <v>46982</v>
       </c>
-      <c r="H196" s="3"/>
+      <c r="H196" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>10</v>
@@ -6431,22 +6595,24 @@
         <v>11</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="F197" s="4">
-        <v>46094</v>
+        <v>44533</v>
       </c>
       <c r="G197" s="4">
-        <v>46825</v>
-      </c>
-      <c r="H197" s="3"/>
+        <v>45263</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>13</v>
@@ -6455,22 +6621,24 @@
         <v>14</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="F198" s="4">
-        <v>46094</v>
+        <v>45313</v>
       </c>
       <c r="G198" s="4">
-        <v>46825</v>
-      </c>
-      <c r="H198" s="3"/>
+        <v>46044</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>15</v>
@@ -6479,7 +6647,7 @@
         <v>14</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="F199" s="4">
         <v>46094</v>
@@ -6487,14 +6655,16 @@
       <c r="G199" s="4">
         <v>46825</v>
       </c>
-      <c r="H199" s="3"/>
+      <c r="H199" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>10</v>
@@ -6503,22 +6673,24 @@
         <v>11</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="F200" s="4">
-        <v>45628</v>
+        <v>44092</v>
       </c>
       <c r="G200" s="4">
-        <v>46358</v>
-      </c>
-      <c r="H200" s="3"/>
+        <v>44822</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>13</v>
@@ -6527,22 +6699,24 @@
         <v>14</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="F201" s="4">
-        <v>45628</v>
+        <v>44854</v>
       </c>
       <c r="G201" s="4">
-        <v>46358</v>
-      </c>
-      <c r="H201" s="3"/>
+        <v>45585</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>15</v>
@@ -6551,7 +6725,7 @@
         <v>14</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="F202" s="4">
         <v>45628</v>
@@ -6559,14 +6733,16 @@
       <c r="G202" s="4">
         <v>46358</v>
       </c>
-      <c r="H202" s="3"/>
+      <c r="H202" s="3" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>10</v>
@@ -6575,7 +6751,7 @@
         <v>11</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="F203" s="4">
         <v>45981</v>
@@ -6584,7 +6760,7 @@
         <v>46711</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
